--- a/UI_Applied_Research/portfolio_evidence.xlsx
+++ b/UI_Applied_Research/portfolio_evidence.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <r>
       <rPr>
@@ -94,22 +94,40 @@
     <t xml:space="preserve">Demonstrate effective negotiation and leadership when balancing diverse stakeholder priorities, ensuring that project objectives remain viable and ethically grounded.</t>
   </si>
   <si>
+    <t xml:space="preserve">I had to negotiate project timeline deliverables and demonstrate leadership by redirecting a sprint after it launched, when after an external stakeholder meeting it became clear that certain deliverables where of greater priority than originally planned. To keep within the project delivery timeframe, it was necessary for me to reconfigure release goals, update the current sprint to reflect these, and relay the information to the team clearly and without disrupting the sprint or project development. 
+In doing this I had to decide whether to first complete this sprint, or to instead simply change direction even though the team had just recently agreed on the sprint goals. Ultimately I decided to change course immediately in order to respect the time and energy resources that could be feasibly allocated to the project, and endeavoured to communicate this clearly and respectably to the team.
+(https://github.com/TortoiseLeaf/laurenk_personal_repository_2025/blob/main/notes/leadership-plan-change.png)</t>
+  </si>
+  <si>
     <t>Security  </t>
   </si>
   <si>
     <t xml:space="preserve">Demonstrate negotiation and leadership skills, effectively balancing diverse stakeholder priorities to maintain viable, ethically grounded project objectives.</t>
   </si>
   <si>
+    <t xml:space="preserve">In changing the course of development by rearranging releases to align with stakeholder needs, this allocated appropriate time to the development of necessary features. 
+This helped to ensure the appropriate considerations and testing can be applied to the features, which strengthens security by frequently testing code for vulnerabilities as evidenced by software quality assurance labs, "By integrating automated tests into Continuous Integration/Continuous Deployment (CI/CD) pipelines, organizations can identify vulnerabilities early and address them promptly." (https://www.betabreakers.com/blog/how-automation-testing-strengthens-software-security-in-a-zero-trust-architecture/)
+It also, by readdressing what is necessary for the minimal viable product (MVP) removed the potential for unnecessary code, which reduced the "attack-surface" of the software by preventing unnecessary features being shipped which could carry potential vulnerabilities. This is important as "Attack surface reduction...aligns with key security frameworks such as NIST 800-53, CIS Controls, and ISO 27001, which all emphasize minimizing exposure as part of a proactive security posture." (https://www.rapid7.com/fundamentals/what-is-attack-surface-reduction-asr/)</t>
+  </si>
+  <si>
     <t>Technical  </t>
   </si>
   <si>
     <t xml:space="preserve">Apply expert-level knowledge from current computing research or industry best practices, proposing novel and viable technical solutions to practical problems.</t>
   </si>
   <si>
+    <t xml:space="preserve">In the MAUIScreenTime project designed to create user emission insights from phone usage data, I chose to use the Android device API to tap into source data already collected by Android. This ensures industy best practices are followed in the collection and storage of the primary data as it is the responsibility of the Android coroporation, and as such will be held under due scrutinty in accordance with international GDPR law and regulation. (Link)
+From a development perspective this follows best practices as the consumption of the API must adhere to the official documentation set out for its use, otherwise the API will be inaccessible and the core functionality of the MAUIScreenTime project will fail.
+The project proposes a novel and viable solution to the practical problem of social media application overuse, which although new is infamously and well documented (Link to study). The novel and viable solution proposed is to calculate the estimated enviromnental cost of using these apps, translating them into their CO2e and relaying the information back to the user, quantifying their use into real world impact and incentivising screen time reduction by offering reduction goals with contributing to conservation events as a tangible reward. (Link to SRS?)</t>
+  </si>
+  <si>
     <t>Sustainability </t>
   </si>
   <si>
     <t xml:space="preserve">Conduct an applied research lifecycle assessment (LCA) comparing software or hardware deployment strategies, clearly identifying the most sustainable option based on empirical data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link LCA doc</t>
   </si>
 </sst>
 </file>
@@ -772,16 +790,22 @@
       <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="D4" s="5" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="5" ht="141" customHeight="1">
       <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" ht="183" customHeight="1">
@@ -789,10 +813,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7" ht="188.25" customHeight="1">
@@ -800,10 +827,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/UI_Applied_Research/portfolio_evidence.xlsx
+++ b/UI_Applied_Research/portfolio_evidence.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <r>
       <rPr>
@@ -75,8 +75,8 @@
     <t xml:space="preserve">Critically assess the commercial and socio-economic impacts of advanced algorithms or emerging technologies, identifying opportunities and forecasting industry adoption trends.</t>
   </si>
   <si>
-    <t xml:space="preserve">From an Agile perspective, advanced algorithms in green house gas (GHG) comupation impact commercial projects by affecting the balance between the flexibility of quick iterative MVP production that incorporates stakeholder feedback, and the rigidity of audit trail requirements by environmental regulations and unchangeable calculation methodologies mandated by GHG protocol standards. This is evidenced in the research sentiment that "applying common agile methodologies [to a carbon-zero agility framework] inevitably introduces feedback ambiguity, which can paralyze decision-making and increase errors" (https://www.sciencedirect.com/science/article/abs/pii/S1364815224001233)
-Emerging carbon-measuring technologies have seen adoption into Agile technologies also, forecasting a necessary merging of the two as industry and regulation moves forward. This is evidenced in the example of Synega, a cloud-based delivery operations framework that is "an agile model designed to embed sustainability into the very fabric of cloud operations." (https://www.synyega.com/insights/blog-cloud-greenops-agile-cycle)
+    <t xml:space="preserve">From an Agile perspective, advanced algorithms in green house gas (GHG) comupation impact commercial projects by affecting the balance between the flexibility of quick iterative MVP production that incorporates stakeholder feedback, and the rigidity of audit trail requirements by environmental regulations and unchangeable calculation methodologies mandated by GHG protocol standards. This is evidenced in the research sentiment that "applying common agile methodologies [to a carbon-zero agility framework] inevitably introduces feedback ambiguity, which can paralyze decision-making and increase errors" (Lv, D. et al. 2024).
+Emerging carbon-measuring technologies have seen adoption into Agile technologies also, forecasting a necessary merging of the two as industry and regulation moves forward. This is evidenced in the example of Synega, a cloud-based delivery operations framework that is "an agile model designed to embed sustainability into the very fabric of cloud operations." (Synyega, 2025).
 </t>
   </si>
   <si>
@@ -84,8 +84,8 @@
   </si>
   <si>
     <t xml:space="preserve">Advanced algorithms used by AI in carbon accounting platforms are making it necessary for companies to measure scope 1-3 emissions with increasing accuracy.
-As this impacts regulation necessary to business, this emerging technology is creating an impact commercially due to rapid enterprise adoption. Especially in supply chain heavy sectors like manufacturing and logistics, evidenced by the Corporate Sustainability Reporting Directive  (https://www.carbon-direct.com/climate-policy-hub/corporate-sustainability-reporting-directive)
-Socio-economically the distribution is unbalanced, with richer countries able to afford the technology and more exploited countries facing fiscal barriers for adoption. It could be the case that in the coming years as these technologies are made mandatory, smaller businesses will be excluded from the global market, unable to adopt the technology necessary to adapt to regulation. This concern is discussed in the Forum on Trade, Enivornment &amp; the SDGs, where it is identified that "Many developing countries have struggled to...acquisition into adaptation and...technology development"  (https://tessforum.org/latest/addressing-the-climate-technology-gap-in-developing-countries-through-effective-technology-transfer)</t>
+As this impacts regulation necessary to business, this emerging technology is creating an impact commercially due to rapid enterprise adoption. Especially in supply chain heavy sectors like manufacturing and logistics, evidenced by the Corporate Sustainability Reporting Directive  (Carbon Direct, 2024).
+Socio-economically the distribution is unbalanced, with richer countries able to afford the technology and more exploited countries facing fiscal barriers for adoption. It could be the case that in the coming years as these technologies are made mandatory, smaller businesses will be excluded from the global market, unable to adopt the technology necessary to adapt to regulation. This concern is discussed in the Forum on Trade, Enivornment &amp; the SDGs, where it is identified that "Many developing countries have struggled to...acquisition into adaptation and...technology development"  (Yu, 2023).</t>
   </si>
   <si>
     <t>Meta-skills  </t>
@@ -106,8 +106,8 @@
   </si>
   <si>
     <t xml:space="preserve">In changing the course of development by rearranging releases to align with stakeholder needs, this allocated appropriate time to the development of necessary features. 
-This helped to ensure the appropriate considerations and testing can be applied to the features, which strengthens security by frequently testing code for vulnerabilities as evidenced by software quality assurance labs, "By integrating automated tests into Continuous Integration/Continuous Deployment (CI/CD) pipelines, organizations can identify vulnerabilities early and address them promptly." (https://www.betabreakers.com/blog/how-automation-testing-strengthens-software-security-in-a-zero-trust-architecture/)
-It also, by readdressing what is necessary for the minimal viable product (MVP) removed the potential for unnecessary code, which reduced the "attack-surface" of the software by preventing unnecessary features being shipped which could carry potential vulnerabilities. This is important as "Attack surface reduction...aligns with key security frameworks such as NIST 800-53, CIS Controls, and ISO 27001, which all emphasize minimizing exposure as part of a proactive security posture." (https://www.rapid7.com/fundamentals/what-is-attack-surface-reduction-asr/)</t>
+This helped to ensure the appropriate considerations and testing can be applied to the features, which strengthens security by frequently testing code for vulnerabilities as evidenced by software quality assurance labs, "By integrating automated tests into Continuous Integration/Continuous Deployment (CI/CD) pipelines, organizations can identify vulnerabilities early and address them promptly." (Beta Breakers, 2024).
+It also, by readdressing what is necessary for the minimal viable product (MVP) removed the potential for unnecessary code, which reduced the "attack-surface" of the software by preventing unnecessary features being shipped which could carry potential vulnerabilities. This is important as "Attack surface reduction...aligns with key security frameworks such as NIST 800-53, CIS Controls, and ISO 27001, which all emphasize minimizing exposure as part of a proactive security posture." (Rapid7, 2026).</t>
   </si>
   <si>
     <t>Technical  </t>
@@ -116,9 +116,9 @@
     <t xml:space="preserve">Apply expert-level knowledge from current computing research or industry best practices, proposing novel and viable technical solutions to practical problems.</t>
   </si>
   <si>
-    <t xml:space="preserve">In the MAUIScreenTime project designed to create user emission insights from phone usage data, I chose to use the Android device API to tap into source data already collected by Android. This ensures industy best practices are followed in the collection and storage of the primary data as it is the responsibility of the Android coroporation, and as such will be held under due scrutinty in accordance with international GDPR law and regulation. (Link)
+    <t xml:space="preserve">In the MAUIScreenTime project designed to create user emission insights from phone usage data, I chose to use the Android device API to tap into source data already collected by Android. This ensures industy best practices are followed in the collection and storage of the primary data as it is the responsibility of the Android coroporation, and as such will be held under due scrutinty in accordance with international GDPR law and regulation. (Android, 2026)
 From a development perspective this follows best practices as the consumption of the API must adhere to the official documentation set out for its use, otherwise the API will be inaccessible and the core functionality of the MAUIScreenTime project will fail.
-The project proposes a novel and viable solution to the practical problem of social media application overuse, which although new is infamously and well documented (Link to study). The novel and viable solution proposed is to calculate the estimated enviromnental cost of using these apps, translating them into their CO2e and relaying the information back to the user, quantifying their use into real world impact and incentivising screen time reduction by offering reduction goals with contributing to conservation events as a tangible reward. (Link to SRS?)</t>
+The project proposes a novel and viable solution to the practical problem of social media application overuse, which although new is infamously and well documented (Miller, 2025). The novel and viable solution proposed is to calculate the estimated enviromnental cost of using these apps, translating them into their CO2e and relaying the information back to the user, quantifying their use into real world impact and incentivising screen time reduction by offering reduction goals with contributing to conservation events as a tangible reward. This is outlined in the project Software Requirements Specification (https://github.com/TortoiseLeaf/laurenk_personal_repository_2025/blob/main/UI_Software_Project_Initiation_and_Planning/SRS_Maui.docx).</t>
   </si>
   <si>
     <t>Sustainability </t>
@@ -127,14 +127,189 @@
     <t xml:space="preserve">Conduct an applied research lifecycle assessment (LCA) comparing software or hardware deployment strategies, clearly identifying the most sustainable option based on empirical data.</t>
   </si>
   <si>
-    <t xml:space="preserve">Link LCA doc</t>
+    <t xml:space="preserve">I conducted an applied reserach lifecycle assessment (LCA) comparing software and hardware
+deployment strategies, to clearly identify the most sustainable option based on empirical data 
+(https://github.com/TortoiseLeaf/laurenk_personal_repository_2025/blob/main/UI_Applied_Research/LCA.docx).</t>
+  </si>
+  <si>
+    <t>References:</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="64"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Lv, D. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color indexed="64"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">et al.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="64"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> (2024) </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color indexed="64"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Carbon-zero agility: Enabling carbon-zero organizations through agile management an.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="64"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">. Available at: https://www.sciencedirect.com/science/article/pii/S1364815224001233 (Accessed: 22 April 2026).
+Synyega (2025) </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color indexed="64"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Blog : The Agile GreenOps Cycle: Optimising Cloud for Sustainability</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="64"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">. Available at: https://www.synyega.com/insights/blog-cloud-greenops-agile-cycle (Accessed: 22 April 2026).
+Carbon Direct (2024) </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color indexed="64"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Corporate Sustainability Reporting Directive - Carbon Direct.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="64"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Available at: https://www.carbon-direct.com/climate-policy-hub/corporate-sustainability-reporting-directive (Accessed: 22 April 2026).
+Yu, Vicente. (2023) </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color indexed="64"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">TESS - Addressing the Climate Technology Gap in Developing Countries Through..</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="64"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">. Available at: https://tessforum.org/latest/addressing-the-climate-technology-gap-in-developing-countries-through-effective-technology-transfer (Accessed: 22 April 2026).
+Beta Breakers (2024) </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color indexed="64"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">How Automation Testing Enhances Security | Beta Breakers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="64"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">. Available at: https://www.betabreakers.com/blog/how-automation-testing-strengthens-software-security-in-a-zero-trust-architecture/ (Accessed: 22 April 2026).
+Rapid7 (2026) </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color indexed="64"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">What is Attack Surface Reduction (ASR)? | CyberSecurity Guide - Rapid7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="64"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">. Available at: https://www.rapid7.com/fundamentals/what-is-attack-surface-reduction-asr/ (Accessed: 22 April 2026).
+Android (2026) </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color indexed="64"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Data protection | Android Enterprise</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="64"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">. Available at: https://www.android.com/enterprise/data-protection/ (Accessed: 22 April 2026).
+Miller, J. (2025) </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color indexed="64"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Social Media Addiction Statistics - Risks, Warnings and Safety (2025)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="64"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">. Available at: https://www.addictionhelp.com/social-media-addiction/statistics/ (Accessed: 22 April 2026).</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -143,6 +318,18 @@
     </font>
     <font>
       <sz val="12.000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16.000000"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12.000000"/>
+      <color indexed="64"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -218,7 +405,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -237,6 +424,10 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -737,11 +928,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="83.8515625"/>
+    <col customWidth="1" min="1" max="1" width="14.28125"/>
+    <col customWidth="1" min="3" max="3" width="112.140625"/>
     <col customWidth="1" min="4" max="4" width="81.140625"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33">
+    <row r="1" ht="16.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -752,7 +944,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="146.25" customHeight="1">
+    <row r="2" ht="290.25" customHeight="1">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -766,7 +958,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="132" customHeight="1">
+    <row r="3" ht="263.25" customHeight="1">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -776,11 +968,11 @@
       <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="110.25" customHeight="1">
+    <row r="4" ht="260.25" customHeight="1">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -790,11 +982,11 @@
       <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" ht="141" customHeight="1">
+    <row r="5" ht="311.25" customHeight="1">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -808,7 +1000,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" ht="183" customHeight="1">
+    <row r="6" ht="268.5" customHeight="1">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -832,8 +1024,18 @@
       <c r="C7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="6" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="9" ht="21">
+      <c r="A9" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" ht="409.5" customHeight="1">
+      <c r="C10" s="8" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/UI_Applied_Research/portfolio_evidence.xlsx
+++ b/UI_Applied_Research/portfolio_evidence.xlsx
@@ -135,174 +135,14 @@
     <t>References:</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="64"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">Lv, D. </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color indexed="64"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">et al.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="64"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> (2024) </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color indexed="64"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">Carbon-zero agility: Enabling carbon-zero organizations through agile management an.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="64"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">. Available at: https://www.sciencedirect.com/science/article/pii/S1364815224001233 (Accessed: 22 April 2026).
-Synyega (2025) </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color indexed="64"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">Blog : The Agile GreenOps Cycle: Optimising Cloud for Sustainability</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="64"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">. Available at: https://www.synyega.com/insights/blog-cloud-greenops-agile-cycle (Accessed: 22 April 2026).
-Carbon Direct (2024) </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color indexed="64"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">Corporate Sustainability Reporting Directive - Carbon Direct.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="64"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> Available at: https://www.carbon-direct.com/climate-policy-hub/corporate-sustainability-reporting-directive (Accessed: 22 April 2026).
-Yu, Vicente. (2023) </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color indexed="64"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">TESS - Addressing the Climate Technology Gap in Developing Countries Through..</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="64"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">. Available at: https://tessforum.org/latest/addressing-the-climate-technology-gap-in-developing-countries-through-effective-technology-transfer (Accessed: 22 April 2026).
-Beta Breakers (2024) </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color indexed="64"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">How Automation Testing Enhances Security | Beta Breakers</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="64"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">. Available at: https://www.betabreakers.com/blog/how-automation-testing-strengthens-software-security-in-a-zero-trust-architecture/ (Accessed: 22 April 2026).
-Rapid7 (2026) </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color indexed="64"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">What is Attack Surface Reduction (ASR)? | CyberSecurity Guide - Rapid7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="64"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">. Available at: https://www.rapid7.com/fundamentals/what-is-attack-surface-reduction-asr/ (Accessed: 22 April 2026).
-Android (2026) </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color indexed="64"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">Data protection | Android Enterprise</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="64"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">. Available at: https://www.android.com/enterprise/data-protection/ (Accessed: 22 April 2026).
-Miller, J. (2025) </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color indexed="64"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">Social Media Addiction Statistics - Risks, Warnings and Safety (2025)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="64"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">. Available at: https://www.addictionhelp.com/social-media-addiction/statistics/ (Accessed: 22 April 2026).</t>
-    </r>
+    <t xml:space="preserve">Android (2026) Data protection | Android Enterprise. Available at: https://www.android.com/enterprise/data-protection/ (Accessed: 16 April 2026).
+Beta Breakers (2024) How Automation Testing Enhances Security | Beta Breakers. Available at: https://www.betabreakers.com/blog/how-automation-testing-strengthens-software-security-in-a-zero-trust-architecture/ (Accessed: 16 April 2026).
+Carbon Direct (2024) Corporate Sustainability Reporting Directive - Carbon Direct. Available at: https://www.carbon-direct.com/climate-policy-hub/corporate-sustainability-reporting-directive (Accessed: 22 April 2026).
+Lv, D. et al. (2024) Carbon-zero agility: Enabling carbon-zero organizations through agile management an.. Available at: https://www.sciencedirect.com/science/article/pii/S1364815224001233 (Accessed: 22 April 2026).
+Miller, J. (2025) Social Media Addiction Statistics - Risks, Warnings and Safety (2025). Available at: https://www.addictionhelp.com/social-media-addiction/statistics/ (Accessed: 16 April 2026).
+Rapid7 (2026) What is Attack Surface Reduction (ASR)? | CyberSecurity Guide - Rapid7. Available at: https://www.rapid7.com/fundamentals/what-is-attack-surface-reduction-asr/ (Accessed: 22 April 2026).
+Synyega (2025) Blog : The Agile GreenOps Cycle: Optimising Cloud for Sustainability. Available at: https://www.synyega.com/insights/blog-cloud-greenops-agile-cycle (Accessed: 22 April 2026).
+Yu, Vicente. (2023) TESS - Addressing the Climate Technology Gap in Developing Countries Through... Available at: https://tessforum.org/latest/addressing-the-climate-technology-gap-in-developing-countries-through-effective-technology-transfer (Accessed: 22 April 2026).</t>
   </si>
 </sst>
 </file>
@@ -1037,6 +877,7 @@
       <c r="C10" s="8" t="s">
         <v>21</v>
       </c>
+      <c r="D10" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>

--- a/UI_Applied_Research/portfolio_evidence.xlsx
+++ b/UI_Applied_Research/portfolio_evidence.xlsx
@@ -85,7 +85,8 @@
   <si>
     <t xml:space="preserve">Advanced algorithms used by AI in carbon accounting platforms are making it necessary for companies to measure scope 1-3 emissions with increasing accuracy.
 As this impacts regulation necessary to business, this emerging technology is creating an impact commercially due to rapid enterprise adoption. Especially in supply chain heavy sectors like manufacturing and logistics, evidenced by the Corporate Sustainability Reporting Directive  (Carbon Direct, 2024).
-Socio-economically the distribution is unbalanced, with richer countries able to afford the technology and more exploited countries facing fiscal barriers for adoption. It could be the case that in the coming years as these technologies are made mandatory, smaller businesses will be excluded from the global market, unable to adopt the technology necessary to adapt to regulation. This concern is discussed in the Forum on Trade, Enivornment &amp; the SDGs, where it is identified that "Many developing countries have struggled to...acquisition into adaptation and...technology development"  (Yu, 2023).</t>
+Socio-economically the distribution is unbalanced, with richer countries able to afford the technology and more exploited countries facing fiscal barriers for adoption. It could be the case that in the coming years as these technologies are made mandatory, smaller businesses will be excluded from the global market, unable to adopt the technology necessary to adapt to regulation. This concern is discussed in the Forum on Trade, Enivornment &amp; the SDGs, where it is identified that "Many developing countries have struggled to...acquisition into adaptation and...technology development"  (Yu, 2023).
+</t>
   </si>
   <si>
     <t>Meta-skills  </t>
@@ -96,7 +97,8 @@
   <si>
     <t xml:space="preserve">I had to negotiate project timeline deliverables and demonstrate leadership by redirecting a sprint after it launched, when after an external stakeholder meeting it became clear that certain deliverables where of greater priority than originally planned. To keep within the project delivery timeframe, it was necessary for me to reconfigure release goals, update the current sprint to reflect these, and relay the information to the team clearly and without disrupting the sprint or project development. 
 In doing this I had to decide whether to first complete this sprint, or to instead simply change direction even though the team had just recently agreed on the sprint goals. Ultimately I decided to change course immediately in order to respect the time and energy resources that could be feasibly allocated to the project, and endeavoured to communicate this clearly and respectably to the team.
-(https://github.com/TortoiseLeaf/laurenk_personal_repository_2025/blob/main/notes/leadership-plan-change.png)</t>
+(https://github.com/TortoiseLeaf/laurenk_personal_repository_2025/blob/main/notes/leadership-plan-change.png)
+</t>
   </si>
   <si>
     <t>Security  </t>
@@ -107,7 +109,8 @@
   <si>
     <t xml:space="preserve">In changing the course of development by rearranging releases to align with stakeholder needs, this allocated appropriate time to the development of necessary features. 
 This helped to ensure the appropriate considerations and testing can be applied to the features, which strengthens security by frequently testing code for vulnerabilities as evidenced by software quality assurance labs, "By integrating automated tests into Continuous Integration/Continuous Deployment (CI/CD) pipelines, organizations can identify vulnerabilities early and address them promptly." (Beta Breakers, 2024).
-It also, by readdressing what is necessary for the minimal viable product (MVP) removed the potential for unnecessary code, which reduced the "attack-surface" of the software by preventing unnecessary features being shipped which could carry potential vulnerabilities. This is important as "Attack surface reduction...aligns with key security frameworks such as NIST 800-53, CIS Controls, and ISO 27001, which all emphasize minimizing exposure as part of a proactive security posture." (Rapid7, 2026).</t>
+It also, by readdressing what is necessary for the minimal viable product (MVP) removed the potential for unnecessary code, which reduced the "attack-surface" of the software by preventing unnecessary features being shipped which could carry potential vulnerabilities. This is important as "Attack surface reduction...aligns with key security frameworks such as NIST 800-53, CIS Controls, and ISO 27001, which all emphasize minimizing exposure as part of a proactive security posture." (Rapid7, 2026).
+</t>
   </si>
   <si>
     <t>Technical  </t>
@@ -118,7 +121,8 @@
   <si>
     <t xml:space="preserve">In the MAUIScreenTime project designed to create user emission insights from phone usage data, I chose to use the Android device API to tap into source data already collected by Android. This ensures industy best practices are followed in the collection and storage of the primary data as it is the responsibility of the Android coroporation, and as such will be held under due scrutinty in accordance with international GDPR law and regulation. (Android, 2026)
 From a development perspective this follows best practices as the consumption of the API must adhere to the official documentation set out for its use, otherwise the API will be inaccessible and the core functionality of the MAUIScreenTime project will fail.
-The project proposes a novel and viable solution to the practical problem of social media application overuse, which although new is infamously and well documented (Miller, 2025). The novel and viable solution proposed is to calculate the estimated enviromnental cost of using these apps, translating them into their CO2e and relaying the information back to the user, quantifying their use into real world impact and incentivising screen time reduction by offering reduction goals with contributing to conservation events as a tangible reward. This is outlined in the project Software Requirements Specification (https://github.com/TortoiseLeaf/laurenk_personal_repository_2025/blob/main/UI_Software_Project_Initiation_and_Planning/SRS_Maui.docx).</t>
+The project proposes a novel and viable solution to the practical problem of social media application overuse, which although new is infamously and well documented (Miller, 2025). The novel and viable solution proposed is to calculate the estimated enviromnental cost of using these apps, translating them into their CO2e and relaying the information back to the user, quantifying their use into real world impact and incentivising screen time reduction by offering reduction goals with contributing to conservation events as a tangible reward. This is outlined in the project Software Requirements Specification (https://github.com/TortoiseLeaf/laurenk_personal_repository_2025/blob/main/UI_Software_Project_Initiation_and_Planning/SRS_Maui.docx).
+</t>
   </si>
   <si>
     <t>Sustainability </t>
@@ -129,7 +133,8 @@
   <si>
     <t xml:space="preserve">I conducted an applied reserach lifecycle assessment (LCA) comparing software and hardware
 deployment strategies, to clearly identify the most sustainable option based on empirical data 
-(https://github.com/TortoiseLeaf/laurenk_personal_repository_2025/blob/main/UI_Applied_Research/LCA.docx).</t>
+(https://github.com/TortoiseLeaf/laurenk_personal_repository_2025/blob/main/UI_Applied_Research/LCA.docx).
+</t>
   </si>
   <si>
     <t>References:</t>
@@ -149,7 +154,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -166,11 +171,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12.000000"/>
-      <color indexed="64"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -262,12 +262,12 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -822,11 +822,11 @@
       <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" ht="311.25" customHeight="1">
+    <row r="5" ht="262.5" customHeight="1">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -840,7 +840,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" ht="268.5" customHeight="1">
+    <row r="6" ht="294" customHeight="1">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -864,20 +864,20 @@
       <c r="C7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" ht="21">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="10" ht="409.5" customHeight="1">
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="6"/>
+      <c r="D10" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
